--- a/ReviewIndex_Final.xlsx
+++ b/ReviewIndex_Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hya21_ic_ac_uk/Documents/PhD/Literature Review/Post-ESA Data Extraction/Extraction/Group Review/GitHubRepo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2178448209088/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_17DC7ED08F79A8D366075C52F37BD272FA45DE2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57623A93-5309-478E-A073-BD8DE057C42E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_17DC7ED08F79A8D366075C52F37BD272FA45DE2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8AC927D-20A4-F54B-A8A1-7644FC4A377C}"/>
   <bookViews>
-    <workbookView xWindow="7728" yWindow="744" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="840" windowWidth="50720" windowHeight="27720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="569">
   <si>
     <t>ID</t>
   </si>
@@ -1725,6 +1725,9 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>Exclude</t>
   </si>
 </sst>
 </file>
@@ -2085,23 +2088,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L91"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49" style="3" customWidth="1"/>
     <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="58.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2139,7 +2142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2177,7 +2180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2209,7 +2212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2247,7 +2250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2346,7 +2349,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -2419,7 +2422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -2492,7 +2495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -2527,7 +2530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -2594,7 +2597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>102</v>
       </c>
@@ -2626,7 +2629,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>109</v>
       </c>
@@ -2661,7 +2664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -2731,10 +2734,10 @@
         <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2772,7 +2775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>134</v>
       </c>
@@ -2810,7 +2813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>142</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -2918,7 +2921,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>162</v>
       </c>
@@ -2956,7 +2959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>182</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>190</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>195</v>
       </c>
@@ -3140,7 +3143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>195</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>203</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>203</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>203</v>
       </c>
@@ -3292,7 +3295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>213</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>219</v>
       </c>
@@ -3365,7 +3368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>228</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>236</v>
       </c>
@@ -3435,7 +3438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>241</v>
       </c>
@@ -3473,7 +3476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>241</v>
       </c>
@@ -3511,7 +3514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>249</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>255</v>
       </c>
@@ -3581,7 +3584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>262</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>268</v>
       </c>
@@ -3651,7 +3654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>273</v>
       </c>
@@ -3686,7 +3689,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>273</v>
       </c>
@@ -3721,7 +3724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>279</v>
       </c>
@@ -3759,7 +3762,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>287</v>
       </c>
@@ -3797,7 +3800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>296</v>
       </c>
@@ -3835,7 +3838,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>303</v>
       </c>
@@ -3873,7 +3876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>310</v>
       </c>
@@ -3911,7 +3914,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>317</v>
       </c>
@@ -3949,7 +3952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>324</v>
       </c>
@@ -3987,7 +3990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="80" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>332</v>
       </c>
@@ -4025,7 +4028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>339</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>344</v>
       </c>
@@ -4098,7 +4101,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>352</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>358</v>
       </c>
@@ -4174,7 +4177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>358</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>367</v>
       </c>
@@ -4250,7 +4253,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>377</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>382</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>389</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>389</v>
       </c>
@@ -4396,7 +4399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>399</v>
       </c>
@@ -4434,7 +4437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>406</v>
       </c>
@@ -4472,7 +4475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>406</v>
       </c>
@@ -4510,7 +4513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>415</v>
       </c>
@@ -4545,7 +4548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>422</v>
       </c>
@@ -4574,7 +4577,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>428</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>437</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>437</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>444</v>
       </c>
@@ -4720,7 +4723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>451</v>
       </c>
@@ -4752,7 +4755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>459</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>466</v>
       </c>
@@ -4822,7 +4825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>473</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>479</v>
       </c>
@@ -4898,7 +4901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>486</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>494</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>494</v>
       </c>
@@ -5012,7 +5015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>502</v>
       </c>
@@ -5050,7 +5053,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>502</v>
       </c>
@@ -5088,7 +5091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>511</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>517</v>
       </c>
@@ -5161,7 +5164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>522</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>522</v>
       </c>
@@ -5237,7 +5240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>530</v>
       </c>
@@ -5275,7 +5278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>537</v>
       </c>
@@ -5310,7 +5313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>544</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>551</v>
       </c>
@@ -5386,7 +5389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>551</v>
       </c>
@@ -5426,19 +5429,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3F1B9B-9ABD-457D-9AEB-01761D30789F}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -5446,7 +5450,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>505</v>
       </c>
@@ -5454,7 +5458,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>540</v>
       </c>
@@ -5470,7 +5474,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -5478,7 +5482,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -5486,7 +5490,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>145</v>
       </c>
@@ -5494,7 +5498,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>347</v>
       </c>
@@ -5510,7 +5514,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>565</v>
       </c>
@@ -5518,7 +5522,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>216</v>
       </c>
@@ -5526,7 +5530,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>431</v>
       </c>
@@ -5534,7 +5538,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -5542,7 +5546,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -5550,7 +5554,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>402</v>
       </c>
@@ -5558,7 +5562,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -5566,7 +5570,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -5574,7 +5578,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>425</v>
       </c>
@@ -5582,7 +5586,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -5590,7 +5594,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>222</v>
       </c>
@@ -5598,7 +5602,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>156</v>
       </c>
@@ -5606,7 +5610,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>231</v>
       </c>
@@ -5614,7 +5618,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>489</v>
       </c>
@@ -5622,7 +5626,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -5630,7 +5634,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>392</v>
       </c>
@@ -5638,7 +5642,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -5646,7 +5650,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>454</v>
       </c>
@@ -5654,7 +5658,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>206</v>
       </c>
@@ -5662,7 +5666,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>469</v>
       </c>
@@ -5670,7 +5674,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>78</v>
       </c>
@@ -5678,7 +5682,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -5686,7 +5690,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>567</v>
       </c>
@@ -5694,7 +5698,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>121</v>
       </c>

--- a/ReviewIndex_Final.xlsx
+++ b/ReviewIndex_Final.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2178448209088/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_17DC7ED08F79A8D366075C52F37BD272FA45DE2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8AC927D-20A4-F54B-A8A1-7644FC4A377C}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_17DC7ED08F79A8D366075C52F37BD272FA45DE2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BA67BA7-CC42-0D48-8350-1CDF90485B74}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="840" windowWidth="50720" windowHeight="27720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="280" yWindow="980" windowWidth="33640" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="CountryRegions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$K$1:$K$91</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
